--- a/exports/golf_prices_20260504.xlsx
+++ b/exports/golf_prices_20260504.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:30</t>
+          <t>2026-05-04 22:44:31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L2" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:30</t>
+          <t>2026-05-04 22:44:31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L3" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -648,7 +648,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:32</t>
+          <t>2026-05-04 22:44:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L4" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:32</t>
+          <t>2026-05-04 22:44:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L5" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -790,7 +790,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:34</t>
+          <t>2026-05-04 22:44:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L6" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -861,7 +861,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:34</t>
+          <t>2026-05-04 22:44:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L7" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -932,7 +932,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:36</t>
+          <t>2026-05-04 22:44:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L8" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1003,7 +1003,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:36</t>
+          <t>2026-05-04 22:44:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L9" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1074,7 +1074,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:38</t>
+          <t>2026-05-04 22:44:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L10" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
@@ -1145,7 +1145,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:38</t>
+          <t>2026-05-04 22:44:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L11" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
@@ -1216,7 +1216,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:40</t>
+          <t>2026-05-04 22:44:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L12" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
@@ -1287,7 +1287,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:40</t>
+          <t>2026-05-04 22:44:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L13" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -1358,7 +1358,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:42</t>
+          <t>2026-05-04 22:44:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L14" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
@@ -1429,7 +1429,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:42</t>
+          <t>2026-05-04 22:44:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L15" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
@@ -1500,7 +1500,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:45</t>
+          <t>2026-05-04 22:44:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L16" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
@@ -1571,7 +1571,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:45</t>
+          <t>2026-05-04 22:44:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L17" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
@@ -1642,7 +1642,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:47</t>
+          <t>2026-05-04 22:44:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L18" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
@@ -1713,7 +1713,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:47</t>
+          <t>2026-05-04 22:44:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L19" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
@@ -1784,7 +1784,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:48</t>
+          <t>2026-05-04 22:44:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L20" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
@@ -1855,7 +1855,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:48</t>
+          <t>2026-05-04 22:44:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L21" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:50</t>
+          <t>2026-05-04 22:44:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L22" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
@@ -1997,7 +1997,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:50</t>
+          <t>2026-05-04 22:44:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L23" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M23" t="b">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:52</t>
+          <t>2026-05-04 22:44:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L24" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M24" t="b">
         <v>1</v>
@@ -2139,7 +2139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:52</t>
+          <t>2026-05-04 22:44:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L25" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
@@ -2210,7 +2210,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:54</t>
+          <t>2026-05-04 22:44:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L26" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M26" t="b">
         <v>1</v>
@@ -2281,7 +2281,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:54</t>
+          <t>2026-05-04 22:44:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>177219</v>
+        <v>176093</v>
       </c>
       <c r="L27" t="n">
-        <v>120.22</v>
+        <v>119.53</v>
       </c>
       <c r="M27" t="b">
         <v>1</v>
@@ -2352,7 +2352,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:56</t>
+          <t>2026-05-04 22:44:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L28" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M28" t="b">
         <v>1</v>
@@ -2423,7 +2423,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:56</t>
+          <t>2026-05-04 22:44:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>146664</v>
+        <v>145732</v>
       </c>
       <c r="L29" t="n">
-        <v>99.5</v>
+        <v>98.92</v>
       </c>
       <c r="M29" t="b">
         <v>1</v>
@@ -2494,7 +2494,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:58</t>
+          <t>2026-05-04 22:44:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L30" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M30" t="b">
         <v>1</v>
@@ -2565,7 +2565,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-04 01:57:58</t>
+          <t>2026-05-04 22:44:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L31" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M31" t="b">
         <v>1</v>
@@ -2636,7 +2636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:00</t>
+          <t>2026-05-04 22:45:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L32" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M32" t="b">
         <v>1</v>
@@ -2707,7 +2707,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:00</t>
+          <t>2026-05-04 22:45:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L33" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M33" t="b">
         <v>1</v>
@@ -2778,7 +2778,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:02</t>
+          <t>2026-05-04 22:45:03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L34" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M34" t="b">
         <v>1</v>
@@ -2849,7 +2849,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:02</t>
+          <t>2026-05-04 22:45:03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L35" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M35" t="b">
         <v>1</v>
@@ -2920,7 +2920,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:04</t>
+          <t>2026-05-04 22:45:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L36" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M36" t="b">
         <v>1</v>
@@ -2991,7 +2991,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:04</t>
+          <t>2026-05-04 22:45:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L37" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M37" t="b">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:06</t>
+          <t>2026-05-04 22:45:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L38" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M38" t="b">
         <v>1</v>
@@ -3133,7 +3133,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:06</t>
+          <t>2026-05-04 22:45:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L39" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M39" t="b">
         <v>1</v>
@@ -3204,7 +3204,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:07</t>
+          <t>2026-05-04 22:45:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L40" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M40" t="b">
         <v>1</v>
@@ -3275,7 +3275,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:07</t>
+          <t>2026-05-04 22:45:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L41" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M41" t="b">
         <v>1</v>
@@ -3346,7 +3346,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:09</t>
+          <t>2026-05-04 22:45:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L42" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M42" t="b">
         <v>1</v>
@@ -3417,7 +3417,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:09</t>
+          <t>2026-05-04 22:45:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3464,10 +3464,10 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L43" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
@@ -3488,7 +3488,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:11</t>
+          <t>2026-05-04 22:45:13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L44" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M44" t="b">
         <v>1</v>
@@ -3559,7 +3559,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:11</t>
+          <t>2026-05-04 22:45:13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L45" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M45" t="b">
         <v>1</v>
@@ -3630,7 +3630,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:13</t>
+          <t>2026-05-04 22:45:15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L46" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M46" t="b">
         <v>1</v>
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:13</t>
+          <t>2026-05-04 22:45:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L47" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -3772,7 +3772,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:15</t>
+          <t>2026-05-04 22:45:18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L48" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M48" t="b">
         <v>1</v>
@@ -3843,7 +3843,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:15</t>
+          <t>2026-05-04 22:45:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L49" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
@@ -3914,7 +3914,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:17</t>
+          <t>2026-05-04 22:45:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L50" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M50" t="b">
         <v>1</v>
@@ -3985,7 +3985,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:17</t>
+          <t>2026-05-04 22:45:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L51" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M51" t="b">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:19</t>
+          <t>2026-05-04 22:45:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L52" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M52" t="b">
         <v>1</v>
@@ -4127,7 +4127,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:19</t>
+          <t>2026-05-04 22:45:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L53" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M53" t="b">
         <v>1</v>
@@ -4198,7 +4198,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:20</t>
+          <t>2026-05-04 22:45:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L54" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M54" t="b">
         <v>1</v>
@@ -4269,7 +4269,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:20</t>
+          <t>2026-05-04 22:45:24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>161941</v>
+        <v>160913</v>
       </c>
       <c r="L55" t="n">
-        <v>109.86</v>
+        <v>109.22</v>
       </c>
       <c r="M55" t="b">
         <v>1</v>
@@ -4340,7 +4340,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:22</t>
+          <t>2026-05-04 22:45:26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>119164</v>
+        <v>88046</v>
       </c>
       <c r="L56" t="n">
-        <v>80.84</v>
+        <v>59.76</v>
       </c>
       <c r="M56" t="b">
         <v>1</v>
@@ -4411,7 +4411,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:22</t>
+          <t>2026-05-04 22:45:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L57" t="n">
-        <v>80.84</v>
+        <v>80.37</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
@@ -4482,7 +4482,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:24</t>
+          <t>2026-05-04 22:45:28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L58" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M58" t="b">
         <v>1</v>
@@ -4553,7 +4553,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:24</t>
+          <t>2026-05-04 22:45:28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L59" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
@@ -4624,7 +4624,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:26</t>
+          <t>2026-05-04 22:45:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L60" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M60" t="b">
         <v>1</v>
@@ -4695,7 +4695,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:26</t>
+          <t>2026-05-04 22:45:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L61" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M61" t="b">
         <v>1</v>
@@ -4766,7 +4766,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:28</t>
+          <t>2026-05-04 22:45:32</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L62" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M62" t="b">
         <v>1</v>
@@ -4837,7 +4837,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:28</t>
+          <t>2026-05-04 22:45:32</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L63" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M63" t="b">
         <v>1</v>
@@ -4908,7 +4908,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:30</t>
+          <t>2026-05-04 22:45:34</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L64" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M64" t="b">
         <v>1</v>
@@ -4979,7 +4979,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:30</t>
+          <t>2026-05-04 22:45:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L65" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M65" t="b">
         <v>1</v>
@@ -5050,7 +5050,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:32</t>
+          <t>2026-05-04 22:45:36</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L66" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M66" t="b">
         <v>1</v>
@@ -5121,7 +5121,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:32</t>
+          <t>2026-05-04 22:45:36</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L67" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M67" t="b">
         <v>1</v>
@@ -5192,7 +5192,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:34</t>
+          <t>2026-05-04 22:45:38</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L68" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M68" t="b">
         <v>1</v>
@@ -5263,7 +5263,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:34</t>
+          <t>2026-05-04 22:45:38</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L69" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M69" t="b">
         <v>1</v>
@@ -5334,7 +5334,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:36</t>
+          <t>2026-05-04 22:45:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L70" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M70" t="b">
         <v>1</v>
@@ -5405,7 +5405,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:36</t>
+          <t>2026-05-04 22:45:40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L71" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M71" t="b">
         <v>1</v>
@@ -5476,7 +5476,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:38</t>
+          <t>2026-05-04 22:45:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L72" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M72" t="b">
         <v>1</v>
@@ -5547,7 +5547,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:38</t>
+          <t>2026-05-04 22:45:42</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L73" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M73" t="b">
         <v>1</v>
@@ -5618,7 +5618,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:40</t>
+          <t>2026-05-04 22:45:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L74" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M74" t="b">
         <v>1</v>
@@ -5689,7 +5689,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:40</t>
+          <t>2026-05-04 22:45:44</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L75" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M75" t="b">
         <v>1</v>
@@ -5760,7 +5760,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:42</t>
+          <t>2026-05-04 22:45:46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L76" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M76" t="b">
         <v>1</v>
@@ -5831,7 +5831,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:42</t>
+          <t>2026-05-04 22:45:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L77" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M77" t="b">
         <v>1</v>
@@ -5902,7 +5902,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:43</t>
+          <t>2026-05-04 22:45:48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L78" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M78" t="b">
         <v>1</v>
@@ -5973,7 +5973,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:43</t>
+          <t>2026-05-04 22:45:48</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L79" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M79" t="b">
         <v>1</v>
@@ -6044,7 +6044,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:45</t>
+          <t>2026-05-04 22:45:50</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L80" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M80" t="b">
         <v>1</v>
@@ -6115,7 +6115,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:45</t>
+          <t>2026-05-04 22:45:50</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L81" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M81" t="b">
         <v>1</v>
@@ -6186,7 +6186,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:47</t>
+          <t>2026-05-04 22:45:52</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L82" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M82" t="b">
         <v>1</v>
@@ -6257,7 +6257,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:47</t>
+          <t>2026-05-04 22:45:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L83" t="n">
-        <v>114.01</v>
+        <v>113.34</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
@@ -6328,7 +6328,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:49</t>
+          <t>2026-05-04 22:45:54</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L84" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M84" t="b">
         <v>1</v>
@@ -6399,7 +6399,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:49</t>
+          <t>2026-05-04 22:45:54</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>128208</v>
+        <v>127394</v>
       </c>
       <c r="L85" t="n">
-        <v>86.98</v>
+        <v>86.47</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
@@ -6470,7 +6470,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:51</t>
+          <t>2026-05-04 22:45:56</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L86" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M86" t="b">
         <v>1</v>
@@ -6541,7 +6541,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:51</t>
+          <t>2026-05-04 22:45:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L87" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
@@ -6612,7 +6612,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:53</t>
+          <t>2026-05-04 22:45:58</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L88" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M88" t="b">
         <v>1</v>
@@ -6683,7 +6683,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:53</t>
+          <t>2026-05-04 22:45:58</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L89" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M89" t="b">
         <v>1</v>
@@ -6754,7 +6754,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:55</t>
+          <t>2026-05-04 22:46:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L90" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M90" t="b">
         <v>1</v>
@@ -6825,7 +6825,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:55</t>
+          <t>2026-05-04 22:46:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L91" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M91" t="b">
         <v>1</v>
@@ -6896,7 +6896,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:57</t>
+          <t>2026-05-04 22:46:02</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L92" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M92" t="b">
         <v>1</v>
@@ -6967,7 +6967,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:57</t>
+          <t>2026-05-04 22:46:02</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L93" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M93" t="b">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-04 01:58:59</t>
+          <t>2026-05-04 22:46:04</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:00</t>
+          <t>2026-05-04 22:46:06</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:02</t>
+          <t>2026-05-04 22:46:08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L96" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M96" t="b">
         <v>1</v>
@@ -7235,7 +7235,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:02</t>
+          <t>2026-05-04 22:46:08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L97" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M97" t="b">
         <v>1</v>
@@ -7306,7 +7306,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:04</t>
+          <t>2026-05-04 22:46:10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L98" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
@@ -7377,7 +7377,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:04</t>
+          <t>2026-05-04 22:46:10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L99" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M99" t="b">
         <v>1</v>
@@ -7448,7 +7448,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:06</t>
+          <t>2026-05-04 22:46:12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L100" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M100" t="b">
         <v>1</v>
@@ -7519,7 +7519,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:06</t>
+          <t>2026-05-04 22:46:12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L101" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M101" t="b">
         <v>1</v>
@@ -7590,7 +7590,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:08</t>
+          <t>2026-05-04 22:46:14</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L102" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M102" t="b">
         <v>1</v>
@@ -7661,7 +7661,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:08</t>
+          <t>2026-05-04 22:46:14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L103" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M103" t="b">
         <v>1</v>
@@ -7732,7 +7732,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:10</t>
+          <t>2026-05-04 22:46:16</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7779,10 +7779,10 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L104" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M104" t="b">
         <v>1</v>
@@ -7803,7 +7803,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:10</t>
+          <t>2026-05-04 22:46:16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L105" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M105" t="b">
         <v>1</v>
@@ -7874,7 +7874,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:12</t>
+          <t>2026-05-04 22:46:18</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7937,7 +7937,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:13</t>
+          <t>2026-05-04 22:46:20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8000,7 +8000,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:15</t>
+          <t>2026-05-04 22:46:22</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L108" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M108" t="b">
         <v>1</v>
@@ -8071,7 +8071,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:15</t>
+          <t>2026-05-04 22:46:22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L109" t="n">
-        <v>93.28</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="M109" t="b">
         <v>1</v>
@@ -8142,7 +8142,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:17</t>
+          <t>2026-05-04 22:46:24</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L110" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M110" t="b">
         <v>1</v>
@@ -8213,7 +8213,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:17</t>
+          <t>2026-05-04 22:46:24</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8260,10 +8260,10 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L111" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M111" t="b">
         <v>1</v>
@@ -8284,7 +8284,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:19</t>
+          <t>2026-05-04 22:46:26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L112" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M112" t="b">
         <v>1</v>
@@ -8355,7 +8355,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:19</t>
+          <t>2026-05-04 22:46:26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L113" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M113" t="b">
         <v>1</v>
@@ -8426,7 +8426,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:21</t>
+          <t>2026-05-04 22:46:28</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L114" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M114" t="b">
         <v>1</v>
@@ -8497,7 +8497,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:21</t>
+          <t>2026-05-04 22:46:28</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8544,10 +8544,10 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L115" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M115" t="b">
         <v>1</v>
@@ -8568,7 +8568,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:23</t>
+          <t>2026-05-04 22:46:30</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8615,10 +8615,10 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L116" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M116" t="b">
         <v>1</v>
@@ -8639,7 +8639,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:23</t>
+          <t>2026-05-04 22:46:30</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8686,10 +8686,10 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L117" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M117" t="b">
         <v>1</v>
@@ -8710,7 +8710,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:24</t>
+          <t>2026-05-04 22:46:32</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8757,10 +8757,10 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L118" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M118" t="b">
         <v>1</v>
@@ -8781,7 +8781,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:24</t>
+          <t>2026-05-04 22:46:32</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8828,10 +8828,10 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L119" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M119" t="b">
         <v>1</v>
@@ -8852,7 +8852,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:26</t>
+          <t>2026-05-04 22:46:34</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L120" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M120" t="b">
         <v>1</v>
@@ -8923,7 +8923,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:26</t>
+          <t>2026-05-04 22:46:34</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L121" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M121" t="b">
         <v>1</v>
@@ -8994,7 +8994,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:28</t>
+          <t>2026-05-04 22:46:36</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L122" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M122" t="b">
         <v>1</v>
@@ -9065,7 +9065,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:28</t>
+          <t>2026-05-04 22:46:36</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L123" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M123" t="b">
         <v>1</v>
@@ -9136,7 +9136,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:30</t>
+          <t>2026-05-04 22:46:38</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9183,10 +9183,10 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L124" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M124" t="b">
         <v>1</v>
@@ -9207,7 +9207,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:30</t>
+          <t>2026-05-04 22:46:38</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L125" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M125" t="b">
         <v>1</v>
@@ -9278,7 +9278,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:32</t>
+          <t>2026-05-04 22:46:40</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9325,10 +9325,10 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L126" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M126" t="b">
         <v>1</v>
@@ -9349,7 +9349,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:32</t>
+          <t>2026-05-04 22:46:40</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9396,10 +9396,10 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L127" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M127" t="b">
         <v>1</v>
@@ -9420,7 +9420,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:34</t>
+          <t>2026-05-04 22:46:42</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L128" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M128" t="b">
         <v>1</v>
@@ -9491,7 +9491,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:34</t>
+          <t>2026-05-04 22:46:42</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9538,10 +9538,10 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L129" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M129" t="b">
         <v>1</v>
@@ -9562,7 +9562,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:36</t>
+          <t>2026-05-04 22:46:44</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L130" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M130" t="b">
         <v>1</v>
@@ -9633,7 +9633,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:36</t>
+          <t>2026-05-04 22:46:44</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L131" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M131" t="b">
         <v>1</v>
@@ -9704,7 +9704,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:38</t>
+          <t>2026-05-04 22:46:46</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L132" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M132" t="b">
         <v>1</v>
@@ -9775,7 +9775,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:38</t>
+          <t>2026-05-04 22:46:46</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L133" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M133" t="b">
         <v>1</v>
@@ -9846,7 +9846,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:39</t>
+          <t>2026-05-04 22:46:48</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9893,10 +9893,10 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L134" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M134" t="b">
         <v>1</v>
@@ -9917,7 +9917,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:39</t>
+          <t>2026-05-04 22:46:48</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9964,10 +9964,10 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L135" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M135" t="b">
         <v>1</v>
@@ -9988,7 +9988,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:41</t>
+          <t>2026-05-04 22:46:50</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L136" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M136" t="b">
         <v>1</v>
@@ -10059,7 +10059,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:41</t>
+          <t>2026-05-04 22:46:50</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>278025</v>
+        <v>276689</v>
       </c>
       <c r="L137" t="n">
-        <v>188.61</v>
+        <v>187.81</v>
       </c>
       <c r="M137" t="b">
         <v>1</v>
@@ -10130,7 +10130,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:43</t>
+          <t>2026-05-04 22:46:52</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>292300</v>
+        <v>294000</v>
       </c>
       <c r="L138" t="n">
-        <v>198.29</v>
+        <v>199.56</v>
       </c>
       <c r="M138" t="b">
         <v>0</v>
@@ -10201,7 +10201,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:44</t>
+          <t>2026-05-04 22:46:53</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10248,7 +10248,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>300666</v>
+        <v>300502</v>
       </c>
       <c r="L139" t="n">
         <v>203.97</v>
@@ -10272,7 +10272,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:45</t>
+          <t>2026-05-04 22:46:54</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L140" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M140" t="b">
         <v>1</v>
@@ -10343,7 +10343,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:45</t>
+          <t>2026-05-04 22:46:54</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L141" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M141" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:47</t>
+          <t>2026-05-04 22:46:56</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L142" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M142" t="b">
         <v>1</v>
@@ -10485,7 +10485,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:47</t>
+          <t>2026-05-04 22:46:56</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10532,10 +10532,10 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L143" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M143" t="b">
         <v>1</v>
@@ -10556,7 +10556,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:48</t>
+          <t>2026-05-04 22:46:58</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10603,10 +10603,10 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L144" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M144" t="b">
         <v>1</v>
@@ -10627,7 +10627,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:48</t>
+          <t>2026-05-04 22:46:58</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10674,10 +10674,10 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L145" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M145" t="b">
         <v>1</v>
@@ -10698,7 +10698,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:50</t>
+          <t>2026-05-04 22:47:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10745,10 +10745,10 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L146" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M146" t="b">
         <v>1</v>
@@ -10769,7 +10769,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:50</t>
+          <t>2026-05-04 22:47:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L147" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M147" t="b">
         <v>1</v>
@@ -10840,7 +10840,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:52</t>
+          <t>2026-05-04 22:47:02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10887,10 +10887,10 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L148" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M148" t="b">
         <v>1</v>
@@ -10911,7 +10911,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:52</t>
+          <t>2026-05-04 22:47:02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10958,10 +10958,10 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L149" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M149" t="b">
         <v>1</v>
@@ -10982,7 +10982,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:54</t>
+          <t>2026-05-04 22:47:04</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11029,10 +11029,10 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L150" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M150" t="b">
         <v>1</v>
@@ -11053,7 +11053,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:54</t>
+          <t>2026-05-04 22:47:04</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11100,10 +11100,10 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L151" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M151" t="b">
         <v>1</v>
@@ -11124,7 +11124,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:56</t>
+          <t>2026-05-04 22:47:06</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L152" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M152" t="b">
         <v>1</v>
@@ -11195,7 +11195,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:56</t>
+          <t>2026-05-04 22:47:06</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L153" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M153" t="b">
         <v>1</v>
@@ -11266,7 +11266,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:58</t>
+          <t>2026-05-04 22:47:08</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L154" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M154" t="b">
         <v>1</v>
@@ -11337,7 +11337,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-05-04 01:59:58</t>
+          <t>2026-05-04 22:47:08</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11384,10 +11384,10 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L155" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M155" t="b">
         <v>1</v>
@@ -11408,7 +11408,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:00</t>
+          <t>2026-05-04 22:47:10</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L156" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M156" t="b">
         <v>1</v>
@@ -11479,7 +11479,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:00</t>
+          <t>2026-05-04 22:47:10</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11526,10 +11526,10 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L157" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M157" t="b">
         <v>1</v>
@@ -11550,7 +11550,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:02</t>
+          <t>2026-05-04 22:47:12</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11597,10 +11597,10 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L158" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M158" t="b">
         <v>1</v>
@@ -11621,7 +11621,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:02</t>
+          <t>2026-05-04 22:47:12</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L159" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M159" t="b">
         <v>1</v>
@@ -11692,7 +11692,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:03</t>
+          <t>2026-05-04 22:47:14</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L160" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M160" t="b">
         <v>1</v>
@@ -11763,7 +11763,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:03</t>
+          <t>2026-05-04 22:47:14</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11810,10 +11810,10 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L161" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M161" t="b">
         <v>1</v>
@@ -11834,7 +11834,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:06</t>
+          <t>2026-05-04 22:47:16</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11881,10 +11881,10 @@
         </is>
       </c>
       <c r="K162" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L162" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M162" t="b">
         <v>1</v>
@@ -11905,7 +11905,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:06</t>
+          <t>2026-05-04 22:47:16</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L163" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M163" t="b">
         <v>1</v>
@@ -11976,7 +11976,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:07</t>
+          <t>2026-05-04 22:47:18</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12023,10 +12023,10 @@
         </is>
       </c>
       <c r="K164" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L164" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M164" t="b">
         <v>1</v>
@@ -12047,7 +12047,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:07</t>
+          <t>2026-05-04 22:47:18</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="K165" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L165" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M165" t="b">
         <v>1</v>
@@ -12118,7 +12118,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:09</t>
+          <t>2026-05-04 22:47:20</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12165,10 +12165,10 @@
         </is>
       </c>
       <c r="K166" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L166" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M166" t="b">
         <v>1</v>
@@ -12189,7 +12189,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:09</t>
+          <t>2026-05-04 22:47:20</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="K167" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L167" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M167" t="b">
         <v>1</v>
@@ -12260,7 +12260,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:11</t>
+          <t>2026-05-04 22:47:21</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="K168" t="n">
-        <v>203800</v>
+        <v>205000</v>
       </c>
       <c r="L168" t="n">
-        <v>138.26</v>
+        <v>139.15</v>
       </c>
       <c r="M168" t="b">
         <v>0</v>
@@ -12331,7 +12331,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:11</t>
+          <t>2026-05-04 22:47:22</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12378,10 +12378,10 @@
         </is>
       </c>
       <c r="K169" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L169" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M169" t="b">
         <v>1</v>
@@ -12402,7 +12402,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:11</t>
+          <t>2026-05-04 22:47:22</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12449,10 +12449,10 @@
         </is>
       </c>
       <c r="K170" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L170" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M170" t="b">
         <v>1</v>
@@ -12473,7 +12473,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:13</t>
+          <t>2026-05-04 22:47:24</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="K171" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L171" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M171" t="b">
         <v>1</v>
@@ -12544,7 +12544,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:13</t>
+          <t>2026-05-04 22:47:24</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12591,10 +12591,10 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L172" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M172" t="b">
         <v>1</v>
@@ -12615,7 +12615,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:15</t>
+          <t>2026-05-04 22:47:26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L173" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M173" t="b">
         <v>1</v>
@@ -12686,7 +12686,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:15</t>
+          <t>2026-05-04 22:47:26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="K174" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L174" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M174" t="b">
         <v>1</v>
@@ -12757,7 +12757,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:17</t>
+          <t>2026-05-04 22:47:27</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12804,10 +12804,10 @@
         </is>
       </c>
       <c r="K175" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L175" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M175" t="b">
         <v>1</v>
@@ -12828,7 +12828,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:17</t>
+          <t>2026-05-04 22:47:27</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12875,10 +12875,10 @@
         </is>
       </c>
       <c r="K176" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L176" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M176" t="b">
         <v>1</v>
@@ -12899,7 +12899,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:19</t>
+          <t>2026-05-04 22:47:30</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12946,10 +12946,10 @@
         </is>
       </c>
       <c r="K177" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L177" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M177" t="b">
         <v>1</v>
@@ -12970,7 +12970,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:19</t>
+          <t>2026-05-04 22:47:30</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L178" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M178" t="b">
         <v>1</v>
@@ -13041,7 +13041,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:21</t>
+          <t>2026-05-04 22:47:32</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13088,10 +13088,10 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L179" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M179" t="b">
         <v>1</v>
@@ -13112,7 +13112,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:21</t>
+          <t>2026-05-04 22:47:32</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13159,10 +13159,10 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L180" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M180" t="b">
         <v>1</v>
@@ -13183,7 +13183,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:22</t>
+          <t>2026-05-04 22:47:34</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13230,10 +13230,10 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L181" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M181" t="b">
         <v>1</v>
@@ -13254,7 +13254,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:22</t>
+          <t>2026-05-04 22:47:34</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="K182" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L182" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M182" t="b">
         <v>1</v>
@@ -13325,7 +13325,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:24</t>
+          <t>2026-05-04 22:47:36</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -13372,10 +13372,10 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L183" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M183" t="b">
         <v>1</v>
@@ -13396,7 +13396,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:24</t>
+          <t>2026-05-04 22:47:36</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -13443,10 +13443,10 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L184" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M184" t="b">
         <v>1</v>
@@ -13467,7 +13467,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:26</t>
+          <t>2026-05-04 22:47:38</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L185" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M185" t="b">
         <v>1</v>
@@ -13538,7 +13538,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:26</t>
+          <t>2026-05-04 22:47:38</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L186" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M186" t="b">
         <v>1</v>
@@ -13609,7 +13609,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:28</t>
+          <t>2026-05-04 22:47:40</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -13656,10 +13656,10 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L187" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M187" t="b">
         <v>1</v>
@@ -13680,7 +13680,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:28</t>
+          <t>2026-05-04 22:47:40</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -13727,10 +13727,10 @@
         </is>
       </c>
       <c r="K188" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L188" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M188" t="b">
         <v>1</v>
@@ -13751,7 +13751,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:30</t>
+          <t>2026-05-04 22:47:42</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13798,10 +13798,10 @@
         </is>
       </c>
       <c r="K189" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L189" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M189" t="b">
         <v>1</v>
@@ -13822,7 +13822,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:30</t>
+          <t>2026-05-04 22:47:42</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -13869,10 +13869,10 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L190" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M190" t="b">
         <v>1</v>
@@ -13893,7 +13893,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:32</t>
+          <t>2026-05-04 22:47:43</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L191" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M191" t="b">
         <v>1</v>
@@ -13964,7 +13964,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:32</t>
+          <t>2026-05-04 22:47:43</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14011,10 +14011,10 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L192" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M192" t="b">
         <v>1</v>
@@ -14035,7 +14035,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:33</t>
+          <t>2026-05-04 22:47:45</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14082,10 +14082,10 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L193" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M193" t="b">
         <v>1</v>
@@ -14106,7 +14106,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:33</t>
+          <t>2026-05-04 22:47:45</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14153,10 +14153,10 @@
         </is>
       </c>
       <c r="K194" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L194" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M194" t="b">
         <v>1</v>
@@ -14177,7 +14177,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:35</t>
+          <t>2026-05-04 22:47:47</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14224,10 +14224,10 @@
         </is>
       </c>
       <c r="K195" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L195" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M195" t="b">
         <v>1</v>
@@ -14248,7 +14248,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:35</t>
+          <t>2026-05-04 22:47:47</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14295,10 +14295,10 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L196" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M196" t="b">
         <v>1</v>
@@ -14319,7 +14319,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:37</t>
+          <t>2026-05-04 22:47:49</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14382,7 +14382,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:38</t>
+          <t>2026-05-04 22:47:49</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14445,7 +14445,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:38</t>
+          <t>2026-05-04 22:47:50</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -14508,7 +14508,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:40</t>
+          <t>2026-05-04 22:47:52</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -14571,7 +14571,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:41</t>
+          <t>2026-05-04 22:47:54</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -14634,7 +14634,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:43</t>
+          <t>2026-05-04 22:47:56</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -14697,7 +14697,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:45</t>
+          <t>2026-05-04 22:47:57</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -14760,7 +14760,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:47</t>
+          <t>2026-05-04 22:47:59</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -14823,7 +14823,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:49</t>
+          <t>2026-05-04 22:48:01</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:50</t>
+          <t>2026-05-04 22:48:03</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -14949,7 +14949,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:52</t>
+          <t>2026-05-04 22:48:05</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15012,7 +15012,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:54</t>
+          <t>2026-05-04 22:48:07</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15075,7 +15075,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:56</t>
+          <t>2026-05-04 22:48:09</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15138,7 +15138,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:58</t>
+          <t>2026-05-04 22:48:11</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -15201,7 +15201,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-05-04 02:00:59</t>
+          <t>2026-05-04 22:48:13</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -15264,7 +15264,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:01</t>
+          <t>2026-05-04 22:48:15</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -15327,7 +15327,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:03</t>
+          <t>2026-05-04 22:48:16</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -15390,7 +15390,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:03</t>
+          <t>2026-05-04 22:48:16</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -15437,10 +15437,10 @@
         </is>
       </c>
       <c r="K214" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L214" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M214" t="b">
         <v>0</v>
@@ -15461,7 +15461,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:03</t>
+          <t>2026-05-04 22:48:16</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="K215" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L215" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M215" t="b">
         <v>0</v>
@@ -15532,7 +15532,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:05</t>
+          <t>2026-05-04 22:48:18</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="K216" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L216" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M216" t="b">
         <v>0</v>
@@ -15603,7 +15603,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:05</t>
+          <t>2026-05-04 22:48:18</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -15650,10 +15650,10 @@
         </is>
       </c>
       <c r="K217" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L217" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M217" t="b">
         <v>0</v>
@@ -15674,7 +15674,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:07</t>
+          <t>2026-05-04 22:48:20</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -15721,10 +15721,10 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L218" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M218" t="b">
         <v>0</v>
@@ -15745,7 +15745,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:07</t>
+          <t>2026-05-04 22:48:20</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -15792,10 +15792,10 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L219" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M219" t="b">
         <v>0</v>
@@ -15816,7 +15816,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:09</t>
+          <t>2026-05-04 22:48:22</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -15863,10 +15863,10 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L220" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M220" t="b">
         <v>0</v>
@@ -15887,7 +15887,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:09</t>
+          <t>2026-05-04 22:48:22</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -15934,10 +15934,10 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L221" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M221" t="b">
         <v>0</v>
@@ -15958,7 +15958,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:11</t>
+          <t>2026-05-04 22:48:24</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16005,10 +16005,10 @@
         </is>
       </c>
       <c r="K222" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L222" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M222" t="b">
         <v>0</v>
@@ -16029,7 +16029,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:12</t>
+          <t>2026-05-04 22:48:26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -16076,10 +16076,10 @@
         </is>
       </c>
       <c r="K223" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L223" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M223" t="b">
         <v>0</v>
@@ -16100,7 +16100,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:14</t>
+          <t>2026-05-04 22:48:28</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -16147,10 +16147,10 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L224" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M224" t="b">
         <v>0</v>
@@ -16171,7 +16171,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:14</t>
+          <t>2026-05-04 22:48:28</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -16218,10 +16218,10 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L225" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M225" t="b">
         <v>0</v>
@@ -16242,7 +16242,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:16</t>
+          <t>2026-05-04 22:48:30</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -16289,10 +16289,10 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L226" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M226" t="b">
         <v>0</v>
@@ -16313,7 +16313,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:16</t>
+          <t>2026-05-04 22:48:30</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L227" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M227" t="b">
         <v>0</v>
@@ -16384,7 +16384,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:18</t>
+          <t>2026-05-04 22:48:33</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -16431,10 +16431,10 @@
         </is>
       </c>
       <c r="K228" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L228" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M228" t="b">
         <v>0</v>
@@ -16455,7 +16455,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:18</t>
+          <t>2026-05-04 22:48:33</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -16502,10 +16502,10 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L229" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M229" t="b">
         <v>0</v>
@@ -16526,7 +16526,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:20</t>
+          <t>2026-05-04 22:48:35</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -16573,10 +16573,10 @@
         </is>
       </c>
       <c r="K230" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L230" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M230" t="b">
         <v>0</v>
@@ -16597,7 +16597,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:20</t>
+          <t>2026-05-04 22:48:35</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L231" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M231" t="b">
         <v>0</v>
@@ -16668,7 +16668,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:22</t>
+          <t>2026-05-04 22:48:37</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -16715,10 +16715,10 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L232" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M232" t="b">
         <v>0</v>
@@ -16739,7 +16739,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:22</t>
+          <t>2026-05-04 22:48:37</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -16786,10 +16786,10 @@
         </is>
       </c>
       <c r="K233" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L233" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M233" t="b">
         <v>0</v>
@@ -16810,7 +16810,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:24</t>
+          <t>2026-05-04 22:48:39</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -16857,10 +16857,10 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L234" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M234" t="b">
         <v>0</v>
@@ -16881,7 +16881,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:26</t>
+          <t>2026-05-04 22:48:40</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -16928,10 +16928,10 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L235" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M235" t="b">
         <v>0</v>
@@ -16952,7 +16952,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:27</t>
+          <t>2026-05-04 22:48:42</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -16999,10 +16999,10 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L236" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M236" t="b">
         <v>0</v>
@@ -17023,7 +17023,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:27</t>
+          <t>2026-05-04 22:48:42</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -17070,10 +17070,10 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>217911</v>
+        <v>216864</v>
       </c>
       <c r="L237" t="n">
-        <v>147.83</v>
+        <v>147.2</v>
       </c>
       <c r="M237" t="b">
         <v>0</v>
@@ -17094,7 +17094,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:29</t>
+          <t>2026-05-04 22:48:44</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -17141,10 +17141,10 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>221500</v>
+        <v>222800</v>
       </c>
       <c r="L238" t="n">
-        <v>150.26</v>
+        <v>151.23</v>
       </c>
       <c r="M238" t="b">
         <v>0</v>
@@ -17165,7 +17165,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:30</t>
+          <t>2026-05-04 22:48:45</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -17212,7 +17212,7 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>229955</v>
+        <v>229830</v>
       </c>
       <c r="L239" t="n">
         <v>156</v>
@@ -17236,7 +17236,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:31</t>
+          <t>2026-05-04 22:48:46</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -17283,10 +17283,10 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L240" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M240" t="b">
         <v>1</v>
@@ -17307,7 +17307,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:31</t>
+          <t>2026-05-04 22:48:46</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -17354,10 +17354,10 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L241" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M241" t="b">
         <v>1</v>
@@ -17378,7 +17378,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:33</t>
+          <t>2026-05-04 22:48:47</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -17425,10 +17425,10 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L242" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M242" t="b">
         <v>1</v>
@@ -17449,7 +17449,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:33</t>
+          <t>2026-05-04 22:48:47</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -17496,10 +17496,10 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L243" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M243" t="b">
         <v>1</v>
@@ -17520,7 +17520,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:34</t>
+          <t>2026-05-04 22:48:50</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -17567,10 +17567,10 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L244" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M244" t="b">
         <v>1</v>
@@ -17591,7 +17591,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:34</t>
+          <t>2026-05-04 22:48:50</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -17638,10 +17638,10 @@
         </is>
       </c>
       <c r="K245" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L245" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M245" t="b">
         <v>1</v>
@@ -17662,7 +17662,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:36</t>
+          <t>2026-05-04 22:48:52</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L246" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M246" t="b">
         <v>1</v>
@@ -17733,7 +17733,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:36</t>
+          <t>2026-05-04 22:48:52</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -17780,10 +17780,10 @@
         </is>
       </c>
       <c r="K247" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L247" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M247" t="b">
         <v>1</v>
@@ -17804,7 +17804,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:38</t>
+          <t>2026-05-04 22:48:54</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -17851,10 +17851,10 @@
         </is>
       </c>
       <c r="K248" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L248" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M248" t="b">
         <v>1</v>
@@ -17875,7 +17875,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:38</t>
+          <t>2026-05-04 22:48:54</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -17922,10 +17922,10 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L249" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M249" t="b">
         <v>1</v>
@@ -17946,7 +17946,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:40</t>
+          <t>2026-05-04 22:48:56</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -17993,10 +17993,10 @@
         </is>
       </c>
       <c r="K250" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L250" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M250" t="b">
         <v>1</v>
@@ -18017,7 +18017,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:40</t>
+          <t>2026-05-04 22:48:56</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -18064,10 +18064,10 @@
         </is>
       </c>
       <c r="K251" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L251" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M251" t="b">
         <v>1</v>
@@ -18088,7 +18088,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:42</t>
+          <t>2026-05-04 22:48:58</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="K252" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L252" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M252" t="b">
         <v>1</v>
@@ -18159,7 +18159,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:42</t>
+          <t>2026-05-04 22:48:58</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -18206,10 +18206,10 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L253" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M253" t="b">
         <v>1</v>
@@ -18230,7 +18230,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:43</t>
+          <t>2026-05-04 22:49:00</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L254" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M254" t="b">
         <v>1</v>
@@ -18301,7 +18301,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:43</t>
+          <t>2026-05-04 22:49:00</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -18348,10 +18348,10 @@
         </is>
       </c>
       <c r="K255" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L255" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M255" t="b">
         <v>1</v>
@@ -18372,7 +18372,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:45</t>
+          <t>2026-05-04 22:49:02</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -18419,10 +18419,10 @@
         </is>
       </c>
       <c r="K256" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L256" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M256" t="b">
         <v>1</v>
@@ -18443,7 +18443,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:45</t>
+          <t>2026-05-04 22:49:02</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -18490,10 +18490,10 @@
         </is>
       </c>
       <c r="K257" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L257" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M257" t="b">
         <v>1</v>
@@ -18514,7 +18514,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:47</t>
+          <t>2026-05-04 22:49:04</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -18561,10 +18561,10 @@
         </is>
       </c>
       <c r="K258" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L258" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M258" t="b">
         <v>1</v>
@@ -18585,7 +18585,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:47</t>
+          <t>2026-05-04 22:49:04</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -18632,10 +18632,10 @@
         </is>
       </c>
       <c r="K259" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L259" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M259" t="b">
         <v>1</v>
@@ -18656,7 +18656,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:49</t>
+          <t>2026-05-04 22:49:06</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -18703,10 +18703,10 @@
         </is>
       </c>
       <c r="K260" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L260" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M260" t="b">
         <v>1</v>
@@ -18727,7 +18727,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:49</t>
+          <t>2026-05-04 22:49:06</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -18774,10 +18774,10 @@
         </is>
       </c>
       <c r="K261" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L261" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M261" t="b">
         <v>1</v>
@@ -18798,7 +18798,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:51</t>
+          <t>2026-05-04 22:49:08</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -18845,10 +18845,10 @@
         </is>
       </c>
       <c r="K262" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L262" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M262" t="b">
         <v>1</v>
@@ -18869,7 +18869,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:51</t>
+          <t>2026-05-04 22:49:08</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -18916,10 +18916,10 @@
         </is>
       </c>
       <c r="K263" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L263" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M263" t="b">
         <v>1</v>
@@ -18940,7 +18940,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:53</t>
+          <t>2026-05-04 22:49:10</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -18987,10 +18987,10 @@
         </is>
       </c>
       <c r="K264" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L264" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M264" t="b">
         <v>1</v>
@@ -19011,7 +19011,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:53</t>
+          <t>2026-05-04 22:49:10</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -19058,10 +19058,10 @@
         </is>
       </c>
       <c r="K265" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L265" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M265" t="b">
         <v>1</v>
@@ -19082,7 +19082,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:55</t>
+          <t>2026-05-04 22:49:12</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -19129,10 +19129,10 @@
         </is>
       </c>
       <c r="K266" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L266" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M266" t="b">
         <v>1</v>
@@ -19153,7 +19153,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:55</t>
+          <t>2026-05-04 22:49:12</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -19200,10 +19200,10 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>172826</v>
+        <v>171996</v>
       </c>
       <c r="L267" t="n">
-        <v>117.24</v>
+        <v>116.74</v>
       </c>
       <c r="M267" t="b">
         <v>1</v>
@@ -19224,7 +19224,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:56</t>
+          <t>2026-05-04 22:49:13</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -19271,10 +19271,10 @@
         </is>
       </c>
       <c r="K268" t="n">
-        <v>203800</v>
+        <v>205000</v>
       </c>
       <c r="L268" t="n">
-        <v>138.26</v>
+        <v>139.15</v>
       </c>
       <c r="M268" t="b">
         <v>0</v>
@@ -19295,7 +19295,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:56</t>
+          <t>2026-05-04 22:49:14</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -19342,10 +19342,10 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L269" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M269" t="b">
         <v>1</v>
@@ -19366,7 +19366,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:56</t>
+          <t>2026-05-04 22:49:14</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -19413,10 +19413,10 @@
         </is>
       </c>
       <c r="K270" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L270" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M270" t="b">
         <v>1</v>
@@ -19437,7 +19437,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:58</t>
+          <t>2026-05-04 22:49:16</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -19484,10 +19484,10 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L271" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M271" t="b">
         <v>1</v>
@@ -19508,7 +19508,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-05-04 02:01:58</t>
+          <t>2026-05-04 22:49:16</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -19555,10 +19555,10 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L272" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M272" t="b">
         <v>1</v>
@@ -19579,7 +19579,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:00</t>
+          <t>2026-05-04 22:49:18</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -19626,10 +19626,10 @@
         </is>
       </c>
       <c r="K273" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L273" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M273" t="b">
         <v>1</v>
@@ -19650,7 +19650,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:00</t>
+          <t>2026-05-04 22:49:18</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -19697,10 +19697,10 @@
         </is>
       </c>
       <c r="K274" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L274" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M274" t="b">
         <v>1</v>
@@ -19721,7 +19721,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:02</t>
+          <t>2026-05-04 22:49:20</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -19768,10 +19768,10 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L275" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M275" t="b">
         <v>1</v>
@@ -19792,7 +19792,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:02</t>
+          <t>2026-05-04 22:49:20</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -19839,10 +19839,10 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L276" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M276" t="b">
         <v>1</v>
@@ -19863,7 +19863,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:04</t>
+          <t>2026-05-04 22:49:22</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -19910,10 +19910,10 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L277" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M277" t="b">
         <v>1</v>
@@ -19934,7 +19934,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:04</t>
+          <t>2026-05-04 22:49:22</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="K278" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L278" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M278" t="b">
         <v>1</v>
@@ -20005,7 +20005,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:06</t>
+          <t>2026-05-04 22:49:24</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L279" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M279" t="b">
         <v>1</v>
@@ -20076,7 +20076,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:06</t>
+          <t>2026-05-04 22:49:24</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="K280" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L280" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M280" t="b">
         <v>1</v>
@@ -20147,7 +20147,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:07</t>
+          <t>2026-05-04 22:49:26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -20194,10 +20194,10 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L281" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M281" t="b">
         <v>1</v>
@@ -20218,7 +20218,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:07</t>
+          <t>2026-05-04 22:49:26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="K282" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L282" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M282" t="b">
         <v>1</v>
@@ -20289,7 +20289,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:09</t>
+          <t>2026-05-04 22:49:27</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -20336,10 +20336,10 @@
         </is>
       </c>
       <c r="K283" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L283" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M283" t="b">
         <v>1</v>
@@ -20360,7 +20360,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:09</t>
+          <t>2026-05-04 22:49:27</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -20407,10 +20407,10 @@
         </is>
       </c>
       <c r="K284" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L284" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M284" t="b">
         <v>1</v>
@@ -20431,7 +20431,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:11</t>
+          <t>2026-05-04 22:49:29</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -20478,10 +20478,10 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L285" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M285" t="b">
         <v>1</v>
@@ -20502,7 +20502,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:11</t>
+          <t>2026-05-04 22:49:29</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -20549,10 +20549,10 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L286" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M286" t="b">
         <v>1</v>
@@ -20573,7 +20573,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:13</t>
+          <t>2026-05-04 22:49:31</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -20620,10 +20620,10 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L287" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M287" t="b">
         <v>1</v>
@@ -20644,7 +20644,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:13</t>
+          <t>2026-05-04 22:49:31</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -20691,10 +20691,10 @@
         </is>
       </c>
       <c r="K288" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L288" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M288" t="b">
         <v>1</v>
@@ -20715,7 +20715,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:15</t>
+          <t>2026-05-04 22:49:33</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -20762,10 +20762,10 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L289" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M289" t="b">
         <v>1</v>
@@ -20786,7 +20786,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:15</t>
+          <t>2026-05-04 22:49:33</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -20833,10 +20833,10 @@
         </is>
       </c>
       <c r="K290" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L290" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M290" t="b">
         <v>1</v>
@@ -20857,7 +20857,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:17</t>
+          <t>2026-05-04 22:49:35</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -20904,10 +20904,10 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L291" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M291" t="b">
         <v>1</v>
@@ -20928,7 +20928,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:17</t>
+          <t>2026-05-04 22:49:35</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -20975,10 +20975,10 @@
         </is>
       </c>
       <c r="K292" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L292" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M292" t="b">
         <v>1</v>
@@ -20999,7 +20999,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:18</t>
+          <t>2026-05-04 22:49:37</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -21046,10 +21046,10 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L293" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M293" t="b">
         <v>1</v>
@@ -21070,7 +21070,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:18</t>
+          <t>2026-05-04 22:49:37</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -21117,10 +21117,10 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L294" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M294" t="b">
         <v>1</v>
@@ -21141,7 +21141,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:21</t>
+          <t>2026-05-04 22:49:39</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -21188,10 +21188,10 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L295" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M295" t="b">
         <v>1</v>
@@ -21212,7 +21212,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:21</t>
+          <t>2026-05-04 22:49:39</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -21259,10 +21259,10 @@
         </is>
       </c>
       <c r="K296" t="n">
-        <v>168318</v>
+        <v>167509</v>
       </c>
       <c r="L296" t="n">
-        <v>114.19</v>
+        <v>113.7</v>
       </c>
       <c r="M296" t="b">
         <v>1</v>
@@ -21283,7 +21283,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:22</t>
+          <t>2026-05-04 22:49:41</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -21346,7 +21346,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:22</t>
+          <t>2026-05-04 22:49:41</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -21409,7 +21409,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:22</t>
+          <t>2026-05-04 22:49:41</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -21472,7 +21472,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:24</t>
+          <t>2026-05-04 22:49:43</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -21535,7 +21535,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:26</t>
+          <t>2026-05-04 22:49:45</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21598,7 +21598,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:28</t>
+          <t>2026-05-04 22:49:47</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -21661,7 +21661,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:30</t>
+          <t>2026-05-04 22:49:49</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:32</t>
+          <t>2026-05-04 22:49:51</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -21787,7 +21787,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:33</t>
+          <t>2026-05-04 22:49:53</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -21850,7 +21850,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:35</t>
+          <t>2026-05-04 22:49:55</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -21913,7 +21913,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:37</t>
+          <t>2026-05-04 22:49:56</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -21976,7 +21976,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:39</t>
+          <t>2026-05-04 22:49:58</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -22039,7 +22039,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:41</t>
+          <t>2026-05-04 22:50:00</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -22102,7 +22102,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:42</t>
+          <t>2026-05-04 22:50:03</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -22165,7 +22165,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:44</t>
+          <t>2026-05-04 22:50:05</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:46</t>
+          <t>2026-05-04 22:50:06</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -22291,7 +22291,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-05-04 02:02:48</t>
+          <t>2026-05-04 22:50:08</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
